--- a/RFQ Generator Beta Version/Templates/OGIT TEMPLATE.xlsx
+++ b/RFQ Generator Beta Version/Templates/OGIT TEMPLATE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\source\repos\RFQ Generator Beta Version\RFQ Generator Beta Version\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43FAF0AE-C7A6-4D08-9347-0A59D3EFE63A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20454509-0B55-42E8-9F15-00601710510E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E219492D-B306-496A-9DE7-BC44B159969A}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">COMMERCIAL!$A$1:$H$52</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">COMMERCIAL!$1:$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">COMMERCIAL!$1:$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>

--- a/RFQ Generator Beta Version/Templates/OGIT TEMPLATE.xlsx
+++ b/RFQ Generator Beta Version/Templates/OGIT TEMPLATE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\source\repos\RFQ Generator Beta Version\RFQ Generator Beta Version\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20454509-0B55-42E8-9F15-00601710510E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AFC3437-C3E0-40DF-A964-D7A121CA22AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E219492D-B306-496A-9DE7-BC44B159969A}"/>
   </bookViews>
@@ -785,67 +785,72 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>150495</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>80010</xdr:rowOff>
+      <xdr:colOff>167640</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>149416</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1002000</xdr:colOff>
+      <xdr:colOff>797175</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>186689</xdr:rowOff>
+      <xdr:rowOff>9821</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5148" name="Text Box 28">
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5DFF67CE-FBC5-8BBF-40BE-CACF79681FE1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A998A6DE-8828-4944-BC04-FA9DB097FA0B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1">
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="150495" y="9864090"/>
-          <a:ext cx="1491585" cy="297179"/>
+          <a:off x="167640" y="9742996"/>
+          <a:ext cx="1269615" cy="241405"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="0" bIns="0" anchor="t" upright="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-MY" sz="1400" b="1" i="0" u="none" strike="noStrike" baseline="0">
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="Vladimir Script" panose="03050402040407070305" pitchFamily="66" charset="0"/>
-            </a:rPr>
-            <a:t>Awang Sulaiman</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>

--- a/RFQ Generator Beta Version/Templates/OGIT TEMPLATE.xlsx
+++ b/RFQ Generator Beta Version/Templates/OGIT TEMPLATE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\source\repos\RFQ Generator Beta Version\RFQ Generator Beta Version\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AFC3437-C3E0-40DF-A964-D7A121CA22AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87C3D528-6904-4D9C-B64A-8132D9FB07CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E219492D-B306-496A-9DE7-BC44B159969A}"/>
   </bookViews>
@@ -408,7 +408,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -481,9 +481,6 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -532,17 +529,14 @@
     <xf numFmtId="4" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -555,9 +549,6 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -596,8 +587,8 @@
       <xdr:rowOff>30480</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1722120</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>30480</xdr:rowOff>
     </xdr:to>
@@ -671,7 +662,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>820035</xdr:colOff>
+      <xdr:colOff>538095</xdr:colOff>
       <xdr:row>44</xdr:row>
       <xdr:rowOff>144780</xdr:rowOff>
     </xdr:to>
@@ -794,7 +785,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>797175</xdr:colOff>
+      <xdr:colOff>515235</xdr:colOff>
       <xdr:row>46</xdr:row>
       <xdr:rowOff>9821</xdr:rowOff>
     </xdr:to>
@@ -1147,14 +1138,14 @@
   <dimension ref="A1:AW150"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="13.44140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="27" style="2" customWidth="1"/>
     <col min="3" max="3" width="4.109375" style="2" customWidth="1"/>
     <col min="4" max="4" width="28.33203125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="10.5546875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="11.44140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="29.5546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.77734375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.6640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="15.77734375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="24.21875" style="1" customWidth="1"/>
     <col min="9" max="9" width="14.6640625" style="2" customWidth="1"/>
     <col min="10" max="10" width="2.33203125" style="2" customWidth="1"/>
     <col min="11" max="18" width="9.109375" style="2" hidden="1" customWidth="1"/>
@@ -1489,16 +1480,16 @@
       <c r="AR8" s="3"/>
     </row>
     <row r="9" spans="1:44" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="60" t="s">
+      <c r="A9" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="60"/>
-      <c r="C9" s="60"/>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
+      <c r="B9" s="58"/>
+      <c r="C9" s="58"/>
+      <c r="D9" s="58"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="58"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
@@ -1603,16 +1594,16 @@
       <c r="AR11" s="3"/>
     </row>
     <row r="12" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="61" t="s">
+      <c r="A12" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="61"/>
-      <c r="C12" s="61"/>
-      <c r="D12" s="61"/>
-      <c r="E12" s="61"/>
-      <c r="F12" s="61"/>
-      <c r="G12" s="61"/>
-      <c r="H12" s="61"/>
+      <c r="B12" s="59"/>
+      <c r="C12" s="59"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
@@ -1691,16 +1682,16 @@
       <c r="D14" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="48" t="s">
+      <c r="E14" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="F14" s="36" t="s">
+      <c r="F14" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="63" t="s">
+      <c r="G14" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="H14" s="63"/>
+      <c r="H14" s="54"/>
     </row>
     <row r="15" spans="1:44" s="34" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="33" t="s">
@@ -1709,108 +1700,104 @@
       <c r="C15" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="D15" s="37" t="s">
+      <c r="D15" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="52"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="63"/>
-      <c r="H15" s="63"/>
-    </row>
-    <row r="16" spans="1:44" s="38" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E15" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="55" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="60" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" s="60"/>
+    </row>
+    <row r="16" spans="1:44" s="37" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="34"/>
-      <c r="C16" s="39"/>
-      <c r="E16" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="G16" s="62" t="s">
-        <v>28</v>
-      </c>
-      <c r="H16" s="62"/>
+      <c r="C16" s="38"/>
       <c r="K16" s="34"/>
     </row>
-    <row r="17" spans="1:49" s="38" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:49" s="37" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="34"/>
-      <c r="C17" s="39"/>
+      <c r="C17" s="38"/>
       <c r="K17" s="34"/>
     </row>
-    <row r="18" spans="1:49" s="38" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:49" s="37" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="34"/>
-      <c r="C18" s="39"/>
+      <c r="C18" s="38"/>
       <c r="K18" s="34"/>
     </row>
-    <row r="19" spans="1:49" s="40" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:49" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="17"/>
       <c r="F19" s="17"/>
-      <c r="H19" s="41"/>
-    </row>
-    <row r="20" spans="1:49" s="43" customFormat="1" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="42" t="s">
+      <c r="H19" s="40"/>
+    </row>
+    <row r="20" spans="1:49" s="42" customFormat="1" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="59" t="s">
+      <c r="B20" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="59"/>
-      <c r="D20" s="59"/>
-      <c r="E20" s="42" t="s">
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="F20" s="50" t="s">
+      <c r="F20" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="G20" s="51" t="s">
+      <c r="G20" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="51" t="s">
+      <c r="H20" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="I20" s="49"/>
-      <c r="J20" s="49"/>
-      <c r="K20" s="49"/>
-      <c r="L20" s="49"/>
-      <c r="M20" s="49"/>
-      <c r="N20" s="49"/>
-      <c r="O20" s="49"/>
-      <c r="P20" s="49"/>
-      <c r="Q20" s="49"/>
-      <c r="R20" s="49"/>
-      <c r="S20" s="49"/>
-      <c r="T20" s="49"/>
-      <c r="U20" s="49"/>
-      <c r="V20" s="49"/>
-      <c r="W20" s="49"/>
-      <c r="X20" s="49"/>
-      <c r="Y20" s="49"/>
-      <c r="Z20" s="49"/>
-      <c r="AA20" s="49"/>
-      <c r="AB20" s="49"/>
-      <c r="AC20" s="49"/>
-      <c r="AD20" s="49"/>
-      <c r="AE20" s="49"/>
-      <c r="AF20" s="49"/>
-      <c r="AG20" s="49"/>
-      <c r="AH20" s="49"/>
-      <c r="AI20" s="49"/>
-      <c r="AJ20" s="49"/>
-      <c r="AK20" s="49"/>
-      <c r="AL20" s="49"/>
-      <c r="AM20" s="49"/>
-      <c r="AN20" s="49"/>
-      <c r="AO20" s="49"/>
-      <c r="AP20" s="49"/>
-      <c r="AQ20" s="49"/>
-      <c r="AR20" s="49"/>
-      <c r="AS20" s="49"/>
-      <c r="AT20" s="49"/>
-      <c r="AU20" s="49"/>
-      <c r="AV20" s="49"/>
-      <c r="AW20" s="49"/>
-    </row>
-    <row r="21" spans="1:49" s="40" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I20" s="48"/>
+      <c r="J20" s="48"/>
+      <c r="K20" s="48"/>
+      <c r="L20" s="48"/>
+      <c r="M20" s="48"/>
+      <c r="N20" s="48"/>
+      <c r="O20" s="48"/>
+      <c r="P20" s="48"/>
+      <c r="Q20" s="48"/>
+      <c r="R20" s="48"/>
+      <c r="S20" s="48"/>
+      <c r="T20" s="48"/>
+      <c r="U20" s="48"/>
+      <c r="V20" s="48"/>
+      <c r="W20" s="48"/>
+      <c r="X20" s="48"/>
+      <c r="Y20" s="48"/>
+      <c r="Z20" s="48"/>
+      <c r="AA20" s="48"/>
+      <c r="AB20" s="48"/>
+      <c r="AC20" s="48"/>
+      <c r="AD20" s="48"/>
+      <c r="AE20" s="48"/>
+      <c r="AF20" s="48"/>
+      <c r="AG20" s="48"/>
+      <c r="AH20" s="48"/>
+      <c r="AI20" s="48"/>
+      <c r="AJ20" s="48"/>
+      <c r="AK20" s="48"/>
+      <c r="AL20" s="48"/>
+      <c r="AM20" s="48"/>
+      <c r="AN20" s="48"/>
+      <c r="AO20" s="48"/>
+      <c r="AP20" s="48"/>
+      <c r="AQ20" s="48"/>
+      <c r="AR20" s="48"/>
+      <c r="AS20" s="48"/>
+      <c r="AT20" s="48"/>
+      <c r="AU20" s="48"/>
+      <c r="AV20" s="48"/>
+      <c r="AW20" s="48"/>
+    </row>
+    <row r="21" spans="1:49" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="17"/>
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
@@ -1861,72 +1848,72 @@
       <c r="AV21" s="17"/>
       <c r="AW21" s="17"/>
     </row>
-    <row r="22" spans="1:49" s="40" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:49" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="62" t="s">
+      <c r="B22" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="62"/>
-      <c r="D22" s="62"/>
+      <c r="C22" s="60"/>
+      <c r="D22" s="60"/>
       <c r="E22" s="33" t="s">
         <v>32</v>
       </c>
       <c r="F22" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="G22" s="44" t="s">
+      <c r="G22" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="H22" s="44" t="s">
+      <c r="H22" s="43" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:49" s="46" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A23" s="45"/>
-      <c r="B23" s="64"/>
-      <c r="C23" s="64"/>
-      <c r="D23" s="64"/>
-      <c r="F23" s="45"/>
-      <c r="H23" s="47"/>
-    </row>
-    <row r="24" spans="1:49" s="46" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A24" s="45"/>
-      <c r="B24" s="53"/>
-      <c r="C24" s="53"/>
-      <c r="D24" s="53"/>
-      <c r="F24" s="58" t="s">
+    <row r="23" spans="1:49" s="45" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A23" s="44"/>
+      <c r="B23" s="61"/>
+      <c r="C23" s="61"/>
+      <c r="D23" s="61"/>
+      <c r="F23" s="44"/>
+      <c r="H23" s="46"/>
+    </row>
+    <row r="24" spans="1:49" s="45" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A24" s="44"/>
+      <c r="B24" s="52"/>
+      <c r="C24" s="52"/>
+      <c r="D24" s="52"/>
+      <c r="F24" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="G24" s="58"/>
-      <c r="H24" s="54" t="s">
+      <c r="G24" s="56"/>
+      <c r="H24" s="53" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:49" ht="22.2" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F25" s="58" t="s">
+      <c r="F25" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="G25" s="58"/>
-      <c r="H25" s="54" t="s">
+      <c r="G25" s="56"/>
+      <c r="H25" s="53" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="26" spans="1:49" s="40" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:49" s="39" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="17"/>
-      <c r="F26" s="58" t="s">
+      <c r="F26" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="G26" s="58"/>
-      <c r="H26" s="44" t="s">
+      <c r="G26" s="56"/>
+      <c r="H26" s="43" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:49" s="46" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A27" s="45"/>
-      <c r="F27" s="45"/>
-      <c r="H27" s="47"/>
+    <row r="27" spans="1:49" s="45" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A27" s="44"/>
+      <c r="F27" s="44"/>
+      <c r="H27" s="46"/>
     </row>
     <row r="28" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="6"/>
@@ -1951,27 +1938,27 @@
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="1:49" s="29" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="55" t="s">
+    <row r="32" spans="1:49" s="29" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A32" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="B32" s="57" t="s">
+      <c r="B32" s="29" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="31.2" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="55" t="s">
+    <row r="33" spans="1:8" s="29" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A33" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="B33" s="57" t="s">
+      <c r="B33" s="29" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="1:8" s="29" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="55" t="s">
+    <row r="34" spans="1:8" s="29" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A34" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="56" t="s">
+      <c r="B34" s="29" t="s">
         <v>44</v>
       </c>
     </row>
@@ -2138,13 +2125,12 @@
       <c r="M150" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="F26:G26"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A12:H12"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G14:H15"/>
+    <mergeCell ref="G15:H15"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="F24:G24"/>
     <mergeCell ref="F25:G25"/>

--- a/RFQ Generator Beta Version/Templates/OGIT TEMPLATE.xlsx
+++ b/RFQ Generator Beta Version/Templates/OGIT TEMPLATE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\source\repos\RFQ Generator Beta Version\RFQ Generator Beta Version\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87C3D528-6904-4D9C-B64A-8132D9FB07CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED1BC0D-7EB0-42D8-B6E7-CC633DC4A9BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E219492D-B306-496A-9DE7-BC44B159969A}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="COMMERCIAL" sheetId="36" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">COMMERCIAL!$A$1:$H$52</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">COMMERCIAL!$A$1:$H$48</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">COMMERCIAL!$1:$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="45">
   <si>
     <t>:</t>
   </si>
@@ -149,19 +149,7 @@
     <t>total_price</t>
   </si>
   <si>
-    <t>summary_total_price</t>
-  </si>
-  <si>
-    <t>SUB TOTAL</t>
-  </si>
-  <si>
     <t>sub_total</t>
-  </si>
-  <si>
-    <t>_discount</t>
-  </si>
-  <si>
-    <t>DISCOUNT</t>
   </si>
   <si>
     <t xml:space="preserve">Validity: </t>
@@ -535,20 +523,20 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -657,13 +645,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>136378</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>538095</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>144780</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -725,7 +713,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>641985</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>163830</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2286000" cy="272119"/>
@@ -780,13 +768,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>149416</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>515235</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>9821</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1135,7 +1123,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DD93CAE-D691-4165-9E84-59A5178DF7EE}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AW150"/>
+  <dimension ref="A1:AW148"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="2" customWidth="1"/>
@@ -1480,16 +1468,16 @@
       <c r="AR8" s="3"/>
     </row>
     <row r="9" spans="1:44" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="58" t="s">
+      <c r="A9" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="58"/>
-      <c r="C9" s="58"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
-      <c r="H9" s="58"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
@@ -1594,16 +1582,16 @@
       <c r="AR11" s="3"/>
     </row>
     <row r="12" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="59" t="s">
+      <c r="A12" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="59"/>
-      <c r="C12" s="59"/>
-      <c r="D12" s="59"/>
-      <c r="E12" s="59"/>
-      <c r="F12" s="59"/>
-      <c r="G12" s="59"/>
-      <c r="H12" s="59"/>
+      <c r="B12" s="58"/>
+      <c r="C12" s="58"/>
+      <c r="D12" s="58"/>
+      <c r="E12" s="58"/>
+      <c r="F12" s="58"/>
+      <c r="G12" s="58"/>
+      <c r="H12" s="58"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
@@ -1709,10 +1697,10 @@
       <c r="F15" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="G15" s="60" t="s">
+      <c r="G15" s="59" t="s">
         <v>28</v>
       </c>
-      <c r="H15" s="60"/>
+      <c r="H15" s="59"/>
     </row>
     <row r="16" spans="1:44" s="37" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="34"/>
@@ -1738,11 +1726,11 @@
       <c r="A20" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="57" t="s">
+      <c r="B20" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="57"/>
-      <c r="D20" s="57"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
       <c r="E20" s="41" t="s">
         <v>31</v>
       </c>
@@ -1852,11 +1840,11 @@
       <c r="A22" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="60" t="s">
+      <c r="B22" s="59" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="60"/>
-      <c r="D22" s="60"/>
+      <c r="C22" s="59"/>
+      <c r="D22" s="59"/>
       <c r="E22" s="33" t="s">
         <v>32</v>
       </c>
@@ -1883,131 +1871,124 @@
       <c r="B24" s="52"/>
       <c r="C24" s="52"/>
       <c r="D24" s="52"/>
-      <c r="F24" s="56" t="s">
+      <c r="F24" s="60" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" s="60"/>
+      <c r="H24" s="53" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:49" s="45" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A25" s="44"/>
+      <c r="F25" s="44"/>
+      <c r="H25" s="46"/>
+    </row>
+    <row r="26" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="6"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="7"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="9"/>
+    </row>
+    <row r="27" spans="1:49" s="29" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="28" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:49" s="29" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="1:49" s="29" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A29" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="G24" s="56"/>
-      <c r="H24" s="53" t="s">
+      <c r="B29" s="29" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:49" s="29" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A30" s="29" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="25" spans="1:49" ht="22.2" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F25" s="56" t="s">
-        <v>40</v>
-      </c>
-      <c r="G25" s="56"/>
-      <c r="H25" s="53" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="26" spans="1:49" s="39" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="17"/>
-      <c r="F26" s="56" t="s">
-        <v>22</v>
-      </c>
-      <c r="G26" s="56"/>
-      <c r="H26" s="43" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="27" spans="1:49" s="45" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A27" s="44"/>
-      <c r="F27" s="44"/>
-      <c r="H27" s="46"/>
-    </row>
-    <row r="28" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="6"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="7"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="9"/>
-    </row>
-    <row r="29" spans="1:49" s="29" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A29" s="28" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:49" s="29" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="B30" s="29" t="s">
+        <v>41</v>
+      </c>
+    </row>
     <row r="31" spans="1:49" s="29" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="29" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B31" s="29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" spans="1:49" s="29" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="29" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B32" s="29" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" s="29" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A33" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="B33" s="29" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" s="29" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A34" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" s="29" t="s">
-        <v>44</v>
-      </c>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="16"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="21"/>
+      <c r="F33" s="16"/>
+      <c r="H33" s="14"/>
+    </row>
+    <row r="34" spans="1:8" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="16"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="21"/>
+      <c r="F34" s="16"/>
+      <c r="H34" s="14"/>
     </row>
     <row r="35" spans="1:8" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="16"/>
+      <c r="A35" s="19" t="s">
+        <v>21</v>
+      </c>
       <c r="B35" s="20"/>
       <c r="C35" s="14"/>
       <c r="D35" s="21"/>
-      <c r="F35" s="16"/>
-      <c r="H35" s="14"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="23"/>
     </row>
     <row r="36" spans="1:8" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="16"/>
-      <c r="B36" s="20"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="21"/>
-      <c r="F36" s="16"/>
-      <c r="H36" s="14"/>
+      <c r="A36" s="31"/>
+      <c r="B36" s="32"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="24"/>
+      <c r="H36" s="25"/>
     </row>
     <row r="37" spans="1:8" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="B37" s="20"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="21"/>
-      <c r="F37" s="22"/>
-      <c r="G37" s="22"/>
-      <c r="H37" s="23"/>
+      <c r="A37" s="16"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="25"/>
     </row>
     <row r="38" spans="1:8" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="31"/>
-      <c r="B38" s="32"/>
-      <c r="C38" s="32"/>
-      <c r="D38" s="32"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="24"/>
-      <c r="H38" s="25"/>
+      <c r="A38" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="B38" s="18"/>
+      <c r="G38" s="26"/>
+      <c r="H38" s="27"/>
     </row>
     <row r="39" spans="1:8" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="16"/>
+      <c r="A39" s="29"/>
+      <c r="B39" s="18"/>
       <c r="G39" s="26"/>
-      <c r="H39" s="25"/>
+      <c r="H39" s="27"/>
     </row>
     <row r="40" spans="1:8" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="29" t="s">
-        <v>16</v>
-      </c>
+      <c r="A40" s="29"/>
       <c r="B40" s="18"/>
       <c r="G40" s="26"/>
       <c r="H40" s="27"/>
@@ -2024,9 +2005,10 @@
       <c r="G42" s="26"/>
       <c r="H42" s="27"/>
     </row>
-    <row r="43" spans="1:8" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="29"/>
       <c r="B43" s="18"/>
+      <c r="E43" s="30"/>
       <c r="G43" s="26"/>
       <c r="H43" s="27"/>
     </row>
@@ -2036,105 +2018,90 @@
       <c r="G44" s="26"/>
       <c r="H44" s="27"/>
     </row>
-    <row r="45" spans="1:8" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="29"/>
+    <row r="45" spans="1:8" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="16"/>
       <c r="B45" s="18"/>
-      <c r="E45" s="30"/>
       <c r="G45" s="26"/>
       <c r="H45" s="27"/>
     </row>
     <row r="46" spans="1:8" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="29"/>
+      <c r="A46" s="19" t="s">
+        <v>17</v>
+      </c>
       <c r="B46" s="18"/>
       <c r="G46" s="26"/>
       <c r="H46" s="27"/>
     </row>
     <row r="47" spans="1:8" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="16"/>
+      <c r="A47" s="19" t="s">
+        <v>19</v>
+      </c>
       <c r="B47" s="18"/>
       <c r="G47" s="26"/>
       <c r="H47" s="27"/>
     </row>
     <row r="48" spans="1:8" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="19" t="s">
-        <v>17</v>
+      <c r="A48" s="18" t="s">
+        <v>18</v>
       </c>
       <c r="B48" s="18"/>
       <c r="G48" s="26"/>
       <c r="H48" s="27"/>
     </row>
     <row r="49" spans="1:8" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="19" t="s">
-        <v>19</v>
-      </c>
+      <c r="A49" s="16"/>
       <c r="B49" s="18"/>
       <c r="G49" s="26"/>
       <c r="H49" s="27"/>
     </row>
     <row r="50" spans="1:8" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="18" t="s">
-        <v>18</v>
-      </c>
+      <c r="A50" s="16"/>
       <c r="B50" s="18"/>
       <c r="G50" s="26"/>
       <c r="H50" s="27"/>
     </row>
-    <row r="51" spans="1:8" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="16"/>
-      <c r="B51" s="18"/>
-      <c r="G51" s="26"/>
-      <c r="H51" s="27"/>
-    </row>
-    <row r="52" spans="1:8" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="16"/>
-      <c r="B52" s="18"/>
-      <c r="G52" s="26"/>
-      <c r="H52" s="27"/>
-    </row>
-    <row r="72" spans="1:8" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="2"/>
-      <c r="B72" s="2"/>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="1"/>
-    </row>
-    <row r="94" spans="1:8" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A94" s="2"/>
-      <c r="B94" s="2"/>
-      <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
-      <c r="F94" s="2"/>
-      <c r="G94" s="2"/>
-      <c r="H94" s="1"/>
-    </row>
-    <row r="116" spans="1:8" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A116" s="2"/>
-      <c r="B116" s="2"/>
-      <c r="C116" s="2"/>
-      <c r="D116" s="2"/>
-      <c r="E116" s="2"/>
-      <c r="F116" s="2"/>
-      <c r="G116" s="2"/>
-      <c r="H116" s="1"/>
-    </row>
-    <row r="150" spans="13:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="M150" s="5"/>
+    <row r="70" spans="1:8" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A70" s="2"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="1"/>
+    </row>
+    <row r="92" spans="1:8" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A92" s="2"/>
+      <c r="B92" s="2"/>
+      <c r="C92" s="2"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
+      <c r="H92" s="1"/>
+    </row>
+    <row r="114" spans="1:8" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A114" s="2"/>
+      <c r="B114" s="2"/>
+      <c r="C114" s="2"/>
+      <c r="D114" s="2"/>
+      <c r="E114" s="2"/>
+      <c r="F114" s="2"/>
+      <c r="G114" s="2"/>
+      <c r="H114" s="1"/>
+    </row>
+    <row r="148" spans="13:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M148" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="F26:G26"/>
+  <mergeCells count="7">
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="B23:D23"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="G15:H15"/>
     <mergeCell ref="B22:D22"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="B23:D23"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
